--- a/pages/Worlds_2023/Master.xlsx
+++ b/pages/Worlds_2023/Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\Worlds_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC0FD9C8-C6D1-41B6-B39E-1A3258638DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB80010-B26D-4717-9E75-FCDACFCE1E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11736" yWindow="408" windowWidth="9612" windowHeight="12504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="252" yWindow="864" windowWidth="9612" windowHeight="12504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
   <si>
     <t>FileName</t>
   </si>
@@ -33,22 +33,190 @@
     <t>Video</t>
   </si>
   <si>
-    <t>https://youtu.be/dHMcRbAmlm0</t>
-  </si>
-  <si>
-    <t>https://youtu.be/ugc_RFTL0p0</t>
-  </si>
-  <si>
-    <t>Campbell_Bunch_test_2</t>
-  </si>
-  <si>
-    <t>26_7_23_AG_Bunch_test</t>
-  </si>
-  <si>
-    <t>26_7_23_CS_Bunch_test</t>
-  </si>
-  <si>
-    <t>26_7_23_TS_Bunch_test</t>
+    <t>31_7_AG_F2k</t>
+  </si>
+  <si>
+    <t>31_7_AG_F4k_R1</t>
+  </si>
+  <si>
+    <t>31_7_AG_F4k_R2</t>
+  </si>
+  <si>
+    <t>31_7_AW_F4k_R1</t>
+  </si>
+  <si>
+    <t>31_7_AW_F4k_R2</t>
+  </si>
+  <si>
+    <t>31_7_BB_F4k_R1</t>
+  </si>
+  <si>
+    <t>31_7_BB_F4k_R2</t>
+  </si>
+  <si>
+    <t>31_7_CS_F2k</t>
+  </si>
+  <si>
+    <t>31_7_CS_F4k_R1</t>
+  </si>
+  <si>
+    <t>31_7_CS_F4k_R2</t>
+  </si>
+  <si>
+    <t>31_7_ES_F4k_R1</t>
+  </si>
+  <si>
+    <t>31_7_ES_F4k_R2</t>
+  </si>
+  <si>
+    <t>31_7_MD_F4k_R1</t>
+  </si>
+  <si>
+    <t>31_7_MD_F4k_R2</t>
+  </si>
+  <si>
+    <t>31_7_NK_F2k</t>
+  </si>
+  <si>
+    <t>31_7_NK_F4k_R1</t>
+  </si>
+  <si>
+    <t>31_7_NK_F4k_R2</t>
+  </si>
+  <si>
+    <t>31_7_TS_F2k</t>
+  </si>
+  <si>
+    <t>31_7_TS_F4k_R1</t>
+  </si>
+  <si>
+    <t>31_7_TS_F4k_R2</t>
+  </si>
+  <si>
+    <t>https://youtu.be/LnZPyXpRwpM</t>
+  </si>
+  <si>
+    <t>https://youtu.be/2LGu6ye-OZQ</t>
+  </si>
+  <si>
+    <t>https://youtu.be/H1SxAgobrek</t>
+  </si>
+  <si>
+    <t>https://youtu.be/4eXOuY8QSJU</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ElvTaaw2sao</t>
+  </si>
+  <si>
+    <t>1_8_AG_F1T</t>
+  </si>
+  <si>
+    <t>1_8_AG_S1T</t>
+  </si>
+  <si>
+    <t>1_8_AW_S1T</t>
+  </si>
+  <si>
+    <t>1_8_BB_S1T</t>
+  </si>
+  <si>
+    <t>1_8_CS_F1T</t>
+  </si>
+  <si>
+    <t>1_8_CS_S1T</t>
+  </si>
+  <si>
+    <t>1_8_EA_F50</t>
+  </si>
+  <si>
+    <t>1_8_EA_WTS_RAC</t>
+  </si>
+  <si>
+    <t>1_8_EA_WTS_Starts</t>
+  </si>
+  <si>
+    <t>1_8_ES_S1T</t>
+  </si>
+  <si>
+    <t>1_8_MD_S1T</t>
+  </si>
+  <si>
+    <t>1_8_NK_F1T</t>
+  </si>
+  <si>
+    <t>1_8_NK_S1T</t>
+  </si>
+  <si>
+    <t>1_8_OK_F50</t>
+  </si>
+  <si>
+    <t>1_8_OK_RAC</t>
+  </si>
+  <si>
+    <t>1_8_OK_WTS_Starts</t>
+  </si>
+  <si>
+    <t>1_8_RP_F50</t>
+  </si>
+  <si>
+    <t>1_8_RP_WTS_RAC</t>
+  </si>
+  <si>
+    <t>1_8_SD_F50</t>
+  </si>
+  <si>
+    <t>1_8_SD_RAC500</t>
+  </si>
+  <si>
+    <t>1_8_SF_F50</t>
+  </si>
+  <si>
+    <t>1_8_SF_WTS_RAC</t>
+  </si>
+  <si>
+    <t>1_8_SF_WTS_Starts</t>
+  </si>
+  <si>
+    <t>1_8_TS_F1T</t>
+  </si>
+  <si>
+    <t>1_8_TS_S1T</t>
+  </si>
+  <si>
+    <t>https://youtu.be/kj0uj_qfEPY</t>
+  </si>
+  <si>
+    <t>https://youtu.be/XcjdDDq3ewU</t>
+  </si>
+  <si>
+    <t>https://youtu.be/IbCE2-3s9fs</t>
+  </si>
+  <si>
+    <t>https://youtu.be/mZhxkSLfrqA</t>
+  </si>
+  <si>
+    <t>1_8_SD_F100</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Sh75vkQ-rdE</t>
+  </si>
+  <si>
+    <t>https://youtu.be/GU3QHtwI6A0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/886swuGoag4</t>
+  </si>
+  <si>
+    <t>https://youtu.be/U_43kMgcHRU</t>
+  </si>
+  <si>
+    <t>https://youtu.be/8sxUkz1XsT8</t>
+  </si>
+  <si>
+    <t>https://youtu.be/6_e6LuyHRdQ</t>
+  </si>
+  <si>
+    <t>https://youtu.be/EMGzc8kcDwo</t>
   </si>
 </sst>
 </file>
@@ -366,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.109375" bestFit="1" customWidth="1"/>
@@ -383,34 +551,364 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
-        <v>2</v>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>56</v>
+      </c>
+      <c r="B41" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/pages/Worlds_2023/Master.xlsx
+++ b/pages/Worlds_2023/Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\Worlds_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB80010-B26D-4717-9E75-FCDACFCE1E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0969FD-D9CC-40BE-A514-FE2FA115F2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="252" yWindow="864" windowWidth="9612" windowHeight="12504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,87 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
   <si>
     <t>FileName</t>
   </si>
   <si>
     <t>Video</t>
-  </si>
-  <si>
-    <t>31_7_AG_F2k</t>
-  </si>
-  <si>
-    <t>31_7_AG_F4k_R1</t>
-  </si>
-  <si>
-    <t>31_7_AG_F4k_R2</t>
-  </si>
-  <si>
-    <t>31_7_AW_F4k_R1</t>
-  </si>
-  <si>
-    <t>31_7_AW_F4k_R2</t>
-  </si>
-  <si>
-    <t>31_7_BB_F4k_R1</t>
-  </si>
-  <si>
-    <t>31_7_BB_F4k_R2</t>
-  </si>
-  <si>
-    <t>31_7_CS_F2k</t>
-  </si>
-  <si>
-    <t>31_7_CS_F4k_R1</t>
-  </si>
-  <si>
-    <t>31_7_CS_F4k_R2</t>
-  </si>
-  <si>
-    <t>31_7_ES_F4k_R1</t>
-  </si>
-  <si>
-    <t>31_7_ES_F4k_R2</t>
-  </si>
-  <si>
-    <t>31_7_MD_F4k_R1</t>
-  </si>
-  <si>
-    <t>31_7_MD_F4k_R2</t>
-  </si>
-  <si>
-    <t>31_7_NK_F2k</t>
-  </si>
-  <si>
-    <t>31_7_NK_F4k_R1</t>
-  </si>
-  <si>
-    <t>31_7_NK_F4k_R2</t>
-  </si>
-  <si>
-    <t>31_7_TS_F2k</t>
-  </si>
-  <si>
-    <t>31_7_TS_F4k_R1</t>
-  </si>
-  <si>
-    <t>31_7_TS_F4k_R2</t>
-  </si>
-  <si>
-    <t>https://youtu.be/LnZPyXpRwpM</t>
-  </si>
-  <si>
-    <t>https://youtu.be/2LGu6ye-OZQ</t>
-  </si>
-  <si>
-    <t>https://youtu.be/H1SxAgobrek</t>
-  </si>
-  <si>
-    <t>https://youtu.be/4eXOuY8QSJU</t>
-  </si>
-  <si>
-    <t>https://youtu.be/ElvTaaw2sao</t>
   </si>
   <si>
     <t>1_8_AG_F1T</t>
@@ -534,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.109375" bestFit="1" customWidth="1"/>
@@ -554,7 +479,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -562,7 +487,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -570,7 +495,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -578,7 +503,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -586,7 +511,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -594,7 +519,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -602,7 +527,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -610,7 +535,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -618,7 +543,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -626,7 +551,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -634,7 +559,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -642,7 +567,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -650,23 +575,20 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -674,23 +596,20 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -698,217 +617,63 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
         <v>29</v>
-      </c>
-      <c r="B24" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
         <v>33</v>
-      </c>
-      <c r="B28" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>44</v>
-      </c>
-      <c r="B39" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>45</v>
-      </c>
-      <c r="B40" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>56</v>
-      </c>
-      <c r="B41" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>46</v>
-      </c>
-      <c r="B42" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>47</v>
-      </c>
-      <c r="B43" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>48</v>
-      </c>
-      <c r="B44" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>49</v>
-      </c>
-      <c r="B45" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>50</v>
-      </c>
-      <c r="B46" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B47" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/pages/Worlds_2023/Master.xlsx
+++ b/pages/Worlds_2023/Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\Worlds_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0969FD-D9CC-40BE-A514-FE2FA115F2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B76B51-B495-4FCB-8E71-CA13A399AA34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="252" yWindow="0" windowWidth="9612" windowHeight="12504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="50">
   <si>
     <t>FileName</t>
   </si>
@@ -142,6 +142,39 @@
   </si>
   <si>
     <t>https://youtu.be/EMGzc8kcDwo</t>
+  </si>
+  <si>
+    <t>3_8_AG_TP_Q</t>
+  </si>
+  <si>
+    <t>3_8_BB_IP_Q</t>
+  </si>
+  <si>
+    <t>3_8_CS_TP_Q</t>
+  </si>
+  <si>
+    <t>3_8_EA_TS_Q</t>
+  </si>
+  <si>
+    <t>3_8_NK_TP_Q</t>
+  </si>
+  <si>
+    <t>3_8_RP_TS_Q</t>
+  </si>
+  <si>
+    <t>3_8_SF_TS_Q</t>
+  </si>
+  <si>
+    <t>3_8_TS_TP_Q</t>
+  </si>
+  <si>
+    <t>https://youtu.be/xdnrdvLVwME</t>
+  </si>
+  <si>
+    <t>https://youtu.be/63pks-zGKqc</t>
+  </si>
+  <si>
+    <t>https://youtu.be/cEuhXhaq-rM</t>
   </si>
 </sst>
 </file>
@@ -459,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.109375" bestFit="1" customWidth="1"/>
@@ -676,6 +709,70 @@
         <v>33</v>
       </c>
     </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pages/Worlds_2023/Master.xlsx
+++ b/pages/Worlds_2023/Master.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\Worlds_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B76B51-B495-4FCB-8E71-CA13A399AA34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC62461-5B50-43C3-8EA7-59F05097D7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="252" yWindow="0" windowWidth="9612" windowHeight="12504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9504" yWindow="0" windowWidth="9612" windowHeight="12504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="56">
   <si>
     <t>FileName</t>
   </si>
@@ -175,6 +186,24 @@
   </si>
   <si>
     <t>https://youtu.be/cEuhXhaq-rM</t>
+  </si>
+  <si>
+    <t>3_8_EA_TS_R1</t>
+  </si>
+  <si>
+    <t>3_8_SF_TS_R1</t>
+  </si>
+  <si>
+    <t>3_8_RP_TS_R1</t>
+  </si>
+  <si>
+    <t>3_8_BB_IP_F</t>
+  </si>
+  <si>
+    <t>https://youtu.be/jN5BZ0WpgDc</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Xj1osb8m4ik</t>
   </si>
 </sst>
 </file>
@@ -492,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.109375" bestFit="1" customWidth="1"/>
@@ -773,6 +802,38 @@
         <v>49</v>
       </c>
     </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>53</v>
+      </c>
+      <c r="B39" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pages/Worlds_2023/Master.xlsx
+++ b/pages/Worlds_2023/Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\Worlds_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC62461-5B50-43C3-8EA7-59F05097D7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3925F22-DAD4-4EA5-9D2F-CD276C645ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9504" yWindow="0" windowWidth="9612" windowHeight="12504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10920" yWindow="0" windowWidth="9612" windowHeight="12504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="60">
   <si>
     <t>FileName</t>
   </si>
@@ -204,6 +204,18 @@
   </si>
   <si>
     <t>https://youtu.be/Xj1osb8m4ik</t>
+  </si>
+  <si>
+    <t>4_8_BB_TP_Q</t>
+  </si>
+  <si>
+    <t>4_8_ES_TP_Q</t>
+  </si>
+  <si>
+    <t>4_8_MD_TP_Q</t>
+  </si>
+  <si>
+    <t>https://youtu.be/TWHI0YDcNzk</t>
   </si>
 </sst>
 </file>
@@ -521,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.109375" bestFit="1" customWidth="1"/>
@@ -834,6 +846,30 @@
         <v>54</v>
       </c>
     </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" t="s">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pages/Worlds_2023/Master.xlsx
+++ b/pages/Worlds_2023/Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\Worlds_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3925F22-DAD4-4EA5-9D2F-CD276C645ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7048F9F-FEF7-4ABE-93C9-58E4F3C5D537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10920" yWindow="0" windowWidth="9612" windowHeight="12504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12504" yWindow="0" windowWidth="9612" windowHeight="12504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="65">
   <si>
     <t>FileName</t>
   </si>
@@ -216,6 +216,21 @@
   </si>
   <si>
     <t>https://youtu.be/TWHI0YDcNzk</t>
+  </si>
+  <si>
+    <t>4_8_AG_TP_R1</t>
+  </si>
+  <si>
+    <t>4_8_NK_TP_R1</t>
+  </si>
+  <si>
+    <t>4_8_TS_TP_R1</t>
+  </si>
+  <si>
+    <t>4_8_CS_TP_R1</t>
+  </si>
+  <si>
+    <t>https://youtu.be/_Jbk5M_6jbU</t>
   </si>
 </sst>
 </file>
@@ -533,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.109375" bestFit="1" customWidth="1"/>
@@ -870,6 +885,38 @@
         <v>59</v>
       </c>
     </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>62</v>
+      </c>
+      <c r="B45" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>63</v>
+      </c>
+      <c r="B46" t="s">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pages/Worlds_2023/Master.xlsx
+++ b/pages/Worlds_2023/Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\Worlds_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7048F9F-FEF7-4ABE-93C9-58E4F3C5D537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739B8F28-9C6D-47E2-A2ED-C932223EFA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12504" yWindow="0" windowWidth="9612" windowHeight="12504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6972" yWindow="4692" windowWidth="9612" windowHeight="12504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="74">
   <si>
     <t>FileName</t>
   </si>
@@ -231,6 +231,33 @@
   </si>
   <si>
     <t>https://youtu.be/_Jbk5M_6jbU</t>
+  </si>
+  <si>
+    <t>5_8_SD_SP_Q</t>
+  </si>
+  <si>
+    <t>5_8_SD_SP_R16</t>
+  </si>
+  <si>
+    <t>5_8_ES_TP_R1</t>
+  </si>
+  <si>
+    <t>5_8_MD_TP_R1</t>
+  </si>
+  <si>
+    <t>5_8_AW_TP_R1</t>
+  </si>
+  <si>
+    <t>5_8_BB_TP_R1</t>
+  </si>
+  <si>
+    <t>https://youtu.be/SPSduTrQse8</t>
+  </si>
+  <si>
+    <t>https://youtu.be/6OcTAWUlbR0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/H-KDj5p95sM</t>
   </si>
 </sst>
 </file>
@@ -548,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.109375" bestFit="1" customWidth="1"/>
@@ -917,6 +944,54 @@
         <v>64</v>
       </c>
     </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>67</v>
+      </c>
+      <c r="B49" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>68</v>
+      </c>
+      <c r="B50" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>69</v>
+      </c>
+      <c r="B51" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>70</v>
+      </c>
+      <c r="B52" t="s">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pages/Worlds_2023/Master.xlsx
+++ b/pages/Worlds_2023/Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\Worlds_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739B8F28-9C6D-47E2-A2ED-C932223EFA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E40E2B-4046-4710-8021-EE1B4832F2AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6972" yWindow="4692" windowWidth="9612" windowHeight="12504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1008" windowWidth="11256" windowHeight="11952" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>FileName</t>
   </si>
@@ -258,6 +258,60 @@
   </si>
   <si>
     <t>https://youtu.be/H-KDj5p95sM</t>
+  </si>
+  <si>
+    <t>5_8_ES_TP_F</t>
+  </si>
+  <si>
+    <t>5_8_MD_TP_F</t>
+  </si>
+  <si>
+    <t>5_8_AW_TP_F</t>
+  </si>
+  <si>
+    <t>5_8_BB_TP_F</t>
+  </si>
+  <si>
+    <t>https://youtu.be/DmxsxS_-gJw</t>
+  </si>
+  <si>
+    <t>5_8_AG_TP_F</t>
+  </si>
+  <si>
+    <t>5_8_CS_TP_F</t>
+  </si>
+  <si>
+    <t>5_8_NK_TP_F</t>
+  </si>
+  <si>
+    <t>5_8_TS_TP_F</t>
+  </si>
+  <si>
+    <t>https://youtu.be/xiW4Wx0YtRM</t>
+  </si>
+  <si>
+    <t>5_8_EA_KE_R16</t>
+  </si>
+  <si>
+    <t>https://youtu.be/79I-5x67Fo8</t>
+  </si>
+  <si>
+    <t>6_8_EA_KE_QF</t>
+  </si>
+  <si>
+    <t>https://youtu.be/seNzi2AlEDg</t>
+  </si>
+  <si>
+    <t>6_8_TS_IP_Q</t>
+  </si>
+  <si>
+    <t>https://youtu.be/kMm4Y9rzpyc</t>
+  </si>
+  <si>
+    <t>https://youtu.be/k380NhorOQg</t>
+  </si>
+  <si>
+    <t>6_8_CS_OM_SC</t>
   </si>
 </sst>
 </file>
@@ -575,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.109375" bestFit="1" customWidth="1"/>
@@ -992,6 +1046,102 @@
         <v>73</v>
       </c>
     </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>74</v>
+      </c>
+      <c r="B53" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>75</v>
+      </c>
+      <c r="B54" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>76</v>
+      </c>
+      <c r="B55" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>77</v>
+      </c>
+      <c r="B56" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>81</v>
+      </c>
+      <c r="B57" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>80</v>
+      </c>
+      <c r="B58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>82</v>
+      </c>
+      <c r="B59" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>79</v>
+      </c>
+      <c r="B60" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>84</v>
+      </c>
+      <c r="B61" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>86</v>
+      </c>
+      <c r="B62" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>88</v>
+      </c>
+      <c r="B63" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>91</v>
+      </c>
+      <c r="B64" t="s">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pages/Worlds_2023/Master.xlsx
+++ b/pages/Worlds_2023/Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\Worlds_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E40E2B-4046-4710-8021-EE1B4832F2AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA95B36-3733-4002-8286-D740A43A0461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1008" windowWidth="11256" windowHeight="11952" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="636" windowWidth="11472" windowHeight="11868" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="102">
   <si>
     <t>FileName</t>
   </si>
@@ -308,10 +308,40 @@
     <t>https://youtu.be/kMm4Y9rzpyc</t>
   </si>
   <si>
-    <t>https://youtu.be/k380NhorOQg</t>
-  </si>
-  <si>
-    <t>6_8_CS_OM_SC</t>
+    <t>https://youtu.be/L9T4gRnuJOk</t>
+  </si>
+  <si>
+    <t>6_8_CS_OM_Tempo</t>
+  </si>
+  <si>
+    <t>6_8_CS_OM_Scratch</t>
+  </si>
+  <si>
+    <t>6_8_CS_OM_Elim</t>
+  </si>
+  <si>
+    <t>6_8_CS_OM_Points</t>
+  </si>
+  <si>
+    <t>https://youtu.be/X4RrOi6bw9o</t>
+  </si>
+  <si>
+    <t>https://youtu.be/bIvxXxZ2HzU</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UQDv36972yw</t>
+  </si>
+  <si>
+    <t>6_8_EA_KE_SF</t>
+  </si>
+  <si>
+    <t>6_8_EA_KE_F</t>
+  </si>
+  <si>
+    <t>https://youtu.be/wZ-3ZGLHlJQ</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ENVeTeTwSj0</t>
   </si>
 </sst>
 </file>
@@ -629,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B69"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.109375" bestFit="1" customWidth="1"/>
@@ -1136,10 +1166,50 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B64" t="s">
         <v>90</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>91</v>
+      </c>
+      <c r="B65" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>93</v>
+      </c>
+      <c r="B66" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>94</v>
+      </c>
+      <c r="B67" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>98</v>
+      </c>
+      <c r="B68" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>99</v>
+      </c>
+      <c r="B69" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/pages/Worlds_2023/Master.xlsx
+++ b/pages/Worlds_2023/Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\Worlds_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA95B36-3733-4002-8286-D740A43A0461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5307A69-836E-4138-9FA2-3DFC19FFDC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="636" windowWidth="11472" windowHeight="11868" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="110">
   <si>
     <t>FileName</t>
   </si>
@@ -342,6 +342,30 @@
   </si>
   <si>
     <t>https://youtu.be/ENVeTeTwSj0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/PrExiTiZh94</t>
+  </si>
+  <si>
+    <t>7_8_SF_SP_Q</t>
+  </si>
+  <si>
+    <t>7_8_EA_SP_Q</t>
+  </si>
+  <si>
+    <t>7_8_SF_SP_R16</t>
+  </si>
+  <si>
+    <t>7_8_EA_SP_R16</t>
+  </si>
+  <si>
+    <t>https://youtu.be/U9lTlIiYh2g</t>
+  </si>
+  <si>
+    <t>https://youtu.be/929B1w28csw</t>
+  </si>
+  <si>
+    <t>https://youtu.be/L0j_a9xWfAE</t>
   </si>
 </sst>
 </file>
@@ -659,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.109375" bestFit="1" customWidth="1"/>
@@ -1212,6 +1236,38 @@
         <v>101</v>
       </c>
     </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>103</v>
+      </c>
+      <c r="B70" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>104</v>
+      </c>
+      <c r="B71" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>105</v>
+      </c>
+      <c r="B72" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>106</v>
+      </c>
+      <c r="B73" t="s">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pages/Worlds_2023/Master.xlsx
+++ b/pages/Worlds_2023/Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\Worlds_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5307A69-836E-4138-9FA2-3DFC19FFDC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89CD38E-9BEF-415A-9D40-44E708122C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="636" windowWidth="11472" windowHeight="11868" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="123">
   <si>
     <t>FileName</t>
   </si>
@@ -366,6 +366,45 @@
   </si>
   <si>
     <t>https://youtu.be/L0j_a9xWfAE</t>
+  </si>
+  <si>
+    <t>8_8_EA_SP_R8</t>
+  </si>
+  <si>
+    <t>8_8_EA_SP_QF_R1</t>
+  </si>
+  <si>
+    <t>8_8_EA_SP_QF_R2</t>
+  </si>
+  <si>
+    <t>8_8_EA_SP_QF_R3</t>
+  </si>
+  <si>
+    <t>8_8_NK_1K_Q</t>
+  </si>
+  <si>
+    <t>8_8_SD_KE_R1</t>
+  </si>
+  <si>
+    <t>8_8_SD_KE_Rep</t>
+  </si>
+  <si>
+    <t>8_8_CS_Mado</t>
+  </si>
+  <si>
+    <t>8_8_AD_Mado</t>
+  </si>
+  <si>
+    <t>https://youtu.be/MXRCfmN9GNQ</t>
+  </si>
+  <si>
+    <t>https://youtu.be/FWtmlmXBk0o</t>
+  </si>
+  <si>
+    <t>https://youtu.be/LR7rxb800Vo</t>
+  </si>
+  <si>
+    <t>https://youtu.be/W6Aq4U-KcLM</t>
   </si>
 </sst>
 </file>
@@ -683,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B73"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.109375" bestFit="1" customWidth="1"/>
@@ -1268,6 +1307,63 @@
         <v>109</v>
       </c>
     </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>111</v>
+      </c>
+      <c r="B75" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>112</v>
+      </c>
+      <c r="B76" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>113</v>
+      </c>
+      <c r="B77" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>114</v>
+      </c>
+      <c r="B78" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>118</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pages/Worlds_2023/Master.xlsx
+++ b/pages/Worlds_2023/Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\Worlds_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89CD38E-9BEF-415A-9D40-44E708122C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12685A79-C739-4118-A33C-BC4C8F8BBB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="636" windowWidth="11472" windowHeight="11868" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -392,9 +392,6 @@
     <t>8_8_CS_Mado</t>
   </si>
   <si>
-    <t>8_8_AD_Mado</t>
-  </si>
-  <si>
     <t>https://youtu.be/MXRCfmN9GNQ</t>
   </si>
   <si>
@@ -405,6 +402,9 @@
   </si>
   <si>
     <t>https://youtu.be/W6Aq4U-KcLM</t>
+  </si>
+  <si>
+    <t>8_8_AG_Mado</t>
   </si>
 </sst>
 </file>
@@ -1317,7 +1317,7 @@
         <v>111</v>
       </c>
       <c r="B75" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
@@ -1325,7 +1325,7 @@
         <v>112</v>
       </c>
       <c r="B76" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
@@ -1333,7 +1333,7 @@
         <v>113</v>
       </c>
       <c r="B77" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
@@ -1341,7 +1341,7 @@
         <v>114</v>
       </c>
       <c r="B78" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
@@ -1361,7 +1361,7 @@
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/pages/Worlds_2023/Master.xlsx
+++ b/pages/Worlds_2023/Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\Worlds_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12685A79-C739-4118-A33C-BC4C8F8BBB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9285FA50-0307-48F3-87F7-6262F1C78B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="636" windowWidth="11472" windowHeight="11868" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="133">
   <si>
     <t>FileName</t>
   </si>
@@ -405,6 +405,36 @@
   </si>
   <si>
     <t>8_8_AG_Mado</t>
+  </si>
+  <si>
+    <t>9_8_SD_KE_QF</t>
+  </si>
+  <si>
+    <t>https://youtu.be/flcuujs_d0k</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sE3B2Qi5qm0</t>
+  </si>
+  <si>
+    <t>https://youtu.be/TFjK5kFF6DQ</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Kk7U7IZR6_s</t>
+  </si>
+  <si>
+    <t>https://youtu.be/M3UmISfTMio</t>
+  </si>
+  <si>
+    <t>9_8_EA_SP_SF_R1</t>
+  </si>
+  <si>
+    <t>9_8_EA_SP_SF_R2</t>
+  </si>
+  <si>
+    <t>https://youtu.be/GuvAqaTMijw</t>
+  </si>
+  <si>
+    <t>https://youtu.be/rJe_1USULpI</t>
   </si>
 </sst>
 </file>
@@ -722,7 +752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B82"/>
+  <dimension ref="A1:B85"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.109375" bestFit="1" customWidth="1"/>
@@ -1311,6 +1341,9 @@
       <c r="A74" t="s">
         <v>110</v>
       </c>
+      <c r="B74" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
@@ -1348,20 +1381,56 @@
       <c r="A79" t="s">
         <v>115</v>
       </c>
+      <c r="B79" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B80" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B81" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>122</v>
+      </c>
+      <c r="B82" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>123</v>
+      </c>
+      <c r="B83" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>129</v>
+      </c>
+      <c r="B84" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>130</v>
+      </c>
+      <c r="B85" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
